--- a/SW/DISPLAY SCREENS.xlsx
+++ b/SW/DISPLAY SCREENS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://schaeffler-my.sharepoint.com/personal/uiv10467_vitesco_com/Documents/Plocha/automatedelectrictestingsystem_aets/SW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://schaeffler-my.sharepoint.com/personal/uiv10467_vitesco_com/Documents/Plocha/AETS/AETS/SW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1233" documentId="8_{D1488593-6CCD-4D42-B221-91528AA5051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22A6D618-77F3-44F2-B890-371D6D92AD2F}"/>
+  <xr:revisionPtr revIDLastSave="1300" documentId="8_{D1488593-6CCD-4D42-B221-91528AA5051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9188476F-3406-40C3-B8DE-87E53B68FE8A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E6C8F8F3-ACBD-40E2-94DA-A7435C16BF12}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{E6C8F8F3-ACBD-40E2-94DA-A7435C16BF12}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="86">
   <si>
     <t>A</t>
   </si>
@@ -290,6 +290,12 @@
   <si>
     <t>TEST OK</t>
   </si>
+  <si>
+    <t>RELAY COUNT LOW</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
 </sst>
 </file>
 
@@ -412,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -452,6 +458,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1880,6 +1889,112 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>77</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Straight Arrow Connector 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A3D6DBE-BE77-4FB2-A842-CCCFBCD18FAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="48539400" y="5867400"/>
+          <a:ext cx="2324100" cy="3314700"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="152400">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2F2E205-78D6-4193-AEA7-07C33D96813C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="59016900" y="1485900"/>
+          <a:ext cx="0" cy="2057400"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="152400">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2200,7 +2315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{497F4F3F-DF2C-4A2F-A59B-E650E6ED4318}">
-  <dimension ref="B3:AV117"/>
+  <dimension ref="B3:AV123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="24.5703125" customWidth="1"/>
@@ -6873,37 +6988,227 @@
       <c r="W117" s="1"/>
       <c r="X117" s="1"/>
     </row>
+    <row r="119" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="B120" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="E120" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O120" s="1"/>
+      <c r="P120" s="1"/>
+      <c r="Q120" s="1"/>
+      <c r="R120" s="1"/>
+      <c r="S120" s="1"/>
+      <c r="T120" s="1"/>
+      <c r="U120" s="1"/>
+      <c r="V120" s="1"/>
+      <c r="W120" s="1"/>
+      <c r="X120" s="1"/>
+    </row>
+    <row r="121" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="B121" s="4"/>
+      <c r="C121" s="5"/>
+      <c r="E121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H121" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O121" s="1"/>
+      <c r="P121" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R121" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S121" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T121" s="1"/>
+      <c r="U121" s="1"/>
+      <c r="V121" s="1"/>
+      <c r="W121" s="1"/>
+      <c r="X121" s="1"/>
+    </row>
+    <row r="122" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="B122" s="4"/>
+      <c r="C122" s="5"/>
+      <c r="E122" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M122" s="1"/>
+      <c r="N122" s="1"/>
+      <c r="O122" s="1"/>
+      <c r="P122" s="1"/>
+      <c r="Q122" s="1"/>
+      <c r="R122" s="1"/>
+      <c r="S122" s="1"/>
+      <c r="T122" s="1"/>
+      <c r="U122" s="1"/>
+      <c r="V122" s="1"/>
+      <c r="W122" s="1"/>
+      <c r="X122" s="1"/>
+    </row>
+    <row r="123" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="6"/>
+      <c r="C123" s="7"/>
+      <c r="E123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O123" s="1"/>
+      <c r="P123" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q123" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R123" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S123" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T123" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U123" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W123" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X123" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="B96:C99"/>
-    <mergeCell ref="B108:C111"/>
-    <mergeCell ref="B102:C105"/>
-    <mergeCell ref="B114:C117"/>
-    <mergeCell ref="Z86:AA89"/>
-    <mergeCell ref="Z74:AA77"/>
-    <mergeCell ref="Z57:AA60"/>
-    <mergeCell ref="Z62:AA65"/>
-    <mergeCell ref="Z69:AA72"/>
-    <mergeCell ref="B80:C83"/>
-    <mergeCell ref="B86:C89"/>
-    <mergeCell ref="B73:C76"/>
-    <mergeCell ref="Z27:AA30"/>
-    <mergeCell ref="Z32:AA35"/>
-    <mergeCell ref="Z37:AA40"/>
-    <mergeCell ref="Z43:AA46"/>
-    <mergeCell ref="Z79:AA82"/>
-    <mergeCell ref="B42:C45"/>
-    <mergeCell ref="B47:C50"/>
-    <mergeCell ref="B52:C55"/>
-    <mergeCell ref="B57:C60"/>
-    <mergeCell ref="B62:C65"/>
-    <mergeCell ref="B68:C71"/>
+  <mergeCells count="30">
+    <mergeCell ref="B120:C123"/>
     <mergeCell ref="B4:C7"/>
     <mergeCell ref="B9:C12"/>
     <mergeCell ref="B27:C30"/>
     <mergeCell ref="Z49:AA52"/>
     <mergeCell ref="B14:C17"/>
     <mergeCell ref="B32:C35"/>
+    <mergeCell ref="B42:C45"/>
+    <mergeCell ref="B47:C50"/>
+    <mergeCell ref="B52:C55"/>
+    <mergeCell ref="B57:C60"/>
+    <mergeCell ref="B62:C65"/>
+    <mergeCell ref="Z27:AA30"/>
+    <mergeCell ref="Z32:AA35"/>
+    <mergeCell ref="Z37:AA40"/>
+    <mergeCell ref="Z43:AA46"/>
+    <mergeCell ref="Z79:AA82"/>
+    <mergeCell ref="Z74:AA77"/>
+    <mergeCell ref="Z57:AA60"/>
+    <mergeCell ref="Z62:AA65"/>
+    <mergeCell ref="Z69:AA72"/>
+    <mergeCell ref="B80:C83"/>
+    <mergeCell ref="B73:C76"/>
+    <mergeCell ref="B68:C71"/>
+    <mergeCell ref="B96:C99"/>
+    <mergeCell ref="B108:C111"/>
+    <mergeCell ref="B102:C105"/>
+    <mergeCell ref="B114:C117"/>
+    <mergeCell ref="Z86:AA89"/>
+    <mergeCell ref="B86:C89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -6977,7 +7282,7 @@
       <c r="DZ17" s="1"/>
       <c r="EA17" s="1"/>
     </row>
-    <row r="18" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
       <c r="DE18" s="4"/>
       <c r="DF18" s="5"/>
       <c r="DH18" s="1"/>
@@ -7024,6 +7329,46 @@
       <c r="EA18" s="1"/>
     </row>
     <row r="19" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="CD19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="CE19" s="3"/>
+      <c r="CG19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="CH19" s="1"/>
+      <c r="CI19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CJ19" s="1"/>
+      <c r="CK19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CL19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="CN19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CP19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="CQ19" s="1"/>
+      <c r="CR19" s="1"/>
+      <c r="CS19" s="1"/>
+      <c r="CT19" s="1"/>
+      <c r="CU19" s="1"/>
+      <c r="CV19" s="1"/>
+      <c r="CW19" s="1"/>
+      <c r="CX19" s="1"/>
+      <c r="CY19" s="1"/>
+      <c r="CZ19" s="1"/>
       <c r="DE19" s="4"/>
       <c r="DF19" s="5"/>
       <c r="DH19" s="1"/>
@@ -7048,6 +7393,54 @@
       <c r="EA19" s="1"/>
     </row>
     <row r="20" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CD20" s="4"/>
+      <c r="CE20" s="5"/>
+      <c r="CG20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="CH20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="CI20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="CJ20" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK20" s="1"/>
+      <c r="CL20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="CM20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="CN20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="CO20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CP20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="CQ20" s="1"/>
+      <c r="CR20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="CS20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CT20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="CU20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV20" s="1"/>
+      <c r="CW20" s="1"/>
+      <c r="CX20" s="1"/>
+      <c r="CY20" s="1"/>
+      <c r="CZ20" s="1"/>
       <c r="DE20" s="6"/>
       <c r="DF20" s="7"/>
       <c r="DH20" s="1"/>
@@ -7071,7 +7464,102 @@
       <c r="DZ20" s="1"/>
       <c r="EA20" s="1"/>
     </row>
-    <row r="22" spans="82:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="CD21" s="4"/>
+      <c r="CE21" s="5"/>
+      <c r="CG21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CH21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CI21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="CJ21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="CK21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="CL21" s="1"/>
+      <c r="CM21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="CN21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="CO21" s="1"/>
+      <c r="CP21" s="1"/>
+      <c r="CQ21" s="1"/>
+      <c r="CR21" s="1"/>
+      <c r="CS21" s="1"/>
+      <c r="CT21" s="1"/>
+      <c r="CU21" s="1"/>
+      <c r="CV21" s="1"/>
+      <c r="CW21" s="1"/>
+      <c r="CX21" s="1"/>
+      <c r="CY21" s="1"/>
+      <c r="CZ21" s="1"/>
+    </row>
+    <row r="22" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CD22" s="6"/>
+      <c r="CE22" s="7"/>
+      <c r="CG22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="CH22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CI22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="CJ22" s="1"/>
+      <c r="CK22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CL22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="CM22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CP22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="CQ22" s="1"/>
+      <c r="CR22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="CS22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="CT22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="CU22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="CW22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="CX22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CY22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="CZ22" s="1"/>
+    </row>
     <row r="23" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
       <c r="DE23" s="8" t="s">
         <v>83</v>
@@ -11579,7 +12067,21 @@
       <c r="BY130" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
+    <mergeCell ref="BC34:BD37"/>
+    <mergeCell ref="BC39:BD42"/>
+    <mergeCell ref="BC55:BD58"/>
+    <mergeCell ref="CD19:CE22"/>
+    <mergeCell ref="DE46:DF49"/>
+    <mergeCell ref="DE51:DF54"/>
+    <mergeCell ref="B67:C70"/>
+    <mergeCell ref="AB64:AC67"/>
+    <mergeCell ref="AB69:AC72"/>
+    <mergeCell ref="CD71:CE74"/>
+    <mergeCell ref="CD76:CE79"/>
+    <mergeCell ref="BC74:BD77"/>
+    <mergeCell ref="CD46:CE49"/>
+    <mergeCell ref="CD51:CE54"/>
     <mergeCell ref="BC127:BD130"/>
     <mergeCell ref="CD28:CE31"/>
     <mergeCell ref="CD34:CE37"/>
@@ -11596,19 +12098,6 @@
     <mergeCell ref="CD59:CE62"/>
     <mergeCell ref="CD64:CE67"/>
     <mergeCell ref="BC68:BD71"/>
-    <mergeCell ref="CD71:CE74"/>
-    <mergeCell ref="CD76:CE79"/>
-    <mergeCell ref="BC74:BD77"/>
-    <mergeCell ref="CD46:CE49"/>
-    <mergeCell ref="CD51:CE54"/>
-    <mergeCell ref="DE46:DF49"/>
-    <mergeCell ref="DE51:DF54"/>
-    <mergeCell ref="B67:C70"/>
-    <mergeCell ref="AB64:AC67"/>
-    <mergeCell ref="AB69:AC72"/>
-    <mergeCell ref="BC34:BD37"/>
-    <mergeCell ref="BC39:BD42"/>
-    <mergeCell ref="BC55:BD58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/SW/DISPLAY SCREENS.xlsx
+++ b/SW/DISPLAY SCREENS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://schaeffler-my.sharepoint.com/personal/uiv10467_vitesco_com/Documents/Plocha/AETS/AETS/SW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uiv10467\OneDrive - Vitesco Technologies\Plocha\AETS\AETS\SW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1300" documentId="8_{D1488593-6CCD-4D42-B221-91528AA5051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9188476F-3406-40C3-B8DE-87E53B68FE8A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811DFCE9-6A9A-453A-A123-52D0C47C4857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{E6C8F8F3-ACBD-40E2-94DA-A7435C16BF12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E6C8F8F3-ACBD-40E2-94DA-A7435C16BF12}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="88">
   <si>
     <t>A</t>
   </si>
@@ -296,6 +296,12 @@
   <si>
     <t>G</t>
   </si>
+  <si>
+    <t>CONNECTIVITY TOP</t>
+  </si>
+  <si>
+    <t>CONNECTIVITY BOT</t>
+  </si>
 </sst>
 </file>
 
@@ -423,6 +429,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -458,9 +467,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1072,15 +1078,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>51</xdr:col>
-      <xdr:colOff>238124</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>357187</xdr:rowOff>
+      <xdr:colOff>238123</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>53</xdr:col>
-      <xdr:colOff>333374</xdr:colOff>
+      <xdr:colOff>285752</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
+      <xdr:rowOff>166689</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1095,12 +1101,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000" flipH="1" flipV="1">
-          <a:off x="31599187" y="21216937"/>
-          <a:ext cx="2571750" cy="1333500"/>
+          <a:off x="30575250" y="31146749"/>
+          <a:ext cx="4572001" cy="1285879"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 100926"/>
+            <a:gd name="adj1" fmla="val 100000"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln w="152400">
@@ -2326,10 +2332,10 @@
   <sheetData>
     <row r="3" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="4"/>
       <c r="E4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2370,8 +2376,8 @@
       <c r="X4" s="1"/>
     </row>
     <row r="5" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
       <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2414,8 +2420,8 @@
       <c r="X5" s="1"/>
     </row>
     <row r="6" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2452,8 +2458,8 @@
       <c r="X6" s="1"/>
     </row>
     <row r="7" spans="2:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
       <c r="E7" s="1" t="s">
         <v>13</v>
       </c>
@@ -2497,10 +2503,10 @@
     </row>
     <row r="8" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="4"/>
       <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
@@ -2543,8 +2549,8 @@
       <c r="X9" s="1"/>
     </row>
     <row r="10" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
@@ -2579,8 +2585,8 @@
       <c r="X10" s="1"/>
     </row>
     <row r="11" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
@@ -2617,8 +2623,8 @@
       <c r="X11" s="1"/>
     </row>
     <row r="12" spans="2:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
@@ -2656,10 +2662,10 @@
     </row>
     <row r="13" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="4"/>
       <c r="E14" s="1" t="s">
         <v>32</v>
       </c>
@@ -2708,8 +2714,8 @@
       <c r="X14" s="1"/>
     </row>
     <row r="15" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
@@ -2748,8 +2754,8 @@
       <c r="X15" s="1"/>
     </row>
     <row r="16" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
@@ -2788,8 +2794,8 @@
       <c r="X16" s="1"/>
     </row>
     <row r="17" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="8"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
@@ -2821,10 +2827,10 @@
     </row>
     <row r="26" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="4"/>
       <c r="E27" s="1" t="s">
         <v>32</v>
       </c>
@@ -2861,10 +2867,10 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-      <c r="Z27" s="2" t="s">
+      <c r="Z27" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AA27" s="3"/>
+      <c r="AA27" s="4"/>
       <c r="AC27" s="1" t="s">
         <v>32</v>
       </c>
@@ -2903,8 +2909,8 @@
       <c r="AV27" s="1"/>
     </row>
     <row r="28" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
@@ -2955,8 +2961,8 @@
       </c>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="5"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="6"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
       <c r="AE28" s="1" t="s">
@@ -2993,8 +2999,8 @@
       <c r="AV28" s="1"/>
     </row>
     <row r="29" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
@@ -3031,8 +3037,8 @@
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="5"/>
+      <c r="Z29" s="5"/>
+      <c r="AA29" s="6"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1" t="s">
@@ -3069,8 +3075,8 @@
       <c r="AV29" s="1"/>
     </row>
     <row r="30" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="6"/>
-      <c r="C30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
@@ -3107,8 +3113,8 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="7"/>
+      <c r="Z30" s="7"/>
+      <c r="AA30" s="8"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
@@ -3132,10 +3138,10 @@
     </row>
     <row r="31" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="3"/>
+      <c r="C32" s="4"/>
       <c r="E32" s="1" t="s">
         <v>32</v>
       </c>
@@ -3174,10 +3180,10 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="Z32" s="2" t="s">
+      <c r="Z32" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AA32" s="3"/>
+      <c r="AA32" s="4"/>
       <c r="AC32" s="1" t="s">
         <v>32</v>
       </c>
@@ -3216,8 +3222,8 @@
       <c r="AV32" s="1"/>
     </row>
     <row r="33" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-      <c r="C33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1" t="s">
@@ -3254,8 +3260,8 @@
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="5"/>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="6"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1" t="s">
@@ -3296,8 +3302,8 @@
       <c r="AV33" s="1"/>
     </row>
     <row r="34" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B34" s="4"/>
-      <c r="C34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
@@ -3334,8 +3340,8 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="5"/>
+      <c r="Z34" s="5"/>
+      <c r="AA34" s="6"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
       <c r="AE34" s="1" t="s">
@@ -3386,8 +3392,8 @@
       <c r="AV34" s="1"/>
     </row>
     <row r="35" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
@@ -3424,8 +3430,8 @@
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
-      <c r="Z35" s="6"/>
-      <c r="AA35" s="7"/>
+      <c r="Z35" s="7"/>
+      <c r="AA35" s="8"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1" t="s">
@@ -3467,10 +3473,10 @@
     </row>
     <row r="36" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="Z37" s="2" t="s">
+      <c r="Z37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA37" s="3"/>
+      <c r="AA37" s="4"/>
       <c r="AC37" s="1" t="s">
         <v>32</v>
       </c>
@@ -3515,8 +3521,8 @@
       <c r="AV37" s="1"/>
     </row>
     <row r="38" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="5"/>
+      <c r="Z38" s="5"/>
+      <c r="AA38" s="6"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1" t="s">
@@ -3559,8 +3565,8 @@
       <c r="AV38" s="1"/>
     </row>
     <row r="39" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="5"/>
+      <c r="Z39" s="5"/>
+      <c r="AA39" s="6"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
@@ -3583,8 +3589,8 @@
       <c r="AV39" s="1"/>
     </row>
     <row r="40" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z40" s="6"/>
-      <c r="AA40" s="7"/>
+      <c r="Z40" s="7"/>
+      <c r="AA40" s="8"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
       <c r="AE40" s="1"/>
@@ -3608,10 +3614,10 @@
     </row>
     <row r="41" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="3"/>
+      <c r="C42" s="4"/>
       <c r="E42" s="1" t="s">
         <v>32</v>
       </c>
@@ -3650,8 +3656,8 @@
       <c r="X42" s="1"/>
     </row>
     <row r="43" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B43" s="4"/>
-      <c r="C43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
@@ -3688,10 +3694,10 @@
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
-      <c r="Z43" s="2" t="s">
+      <c r="Z43" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AA43" s="3"/>
+      <c r="AA43" s="4"/>
       <c r="AC43" s="1" t="s">
         <v>32</v>
       </c>
@@ -3730,8 +3736,8 @@
       <c r="AV43" s="1"/>
     </row>
     <row r="44" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B44" s="4"/>
-      <c r="C44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
@@ -3774,8 +3780,8 @@
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="5"/>
+      <c r="Z44" s="5"/>
+      <c r="AA44" s="6"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1" t="s">
@@ -3816,8 +3822,8 @@
       <c r="AV44" s="1"/>
     </row>
     <row r="45" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="6"/>
-      <c r="C45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="8"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -3838,8 +3844,8 @@
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="5"/>
+      <c r="Z45" s="5"/>
+      <c r="AA45" s="6"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1" t="s">
@@ -3880,8 +3886,8 @@
       <c r="AV45" s="1"/>
     </row>
     <row r="46" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="7"/>
+      <c r="Z46" s="7"/>
+      <c r="AA46" s="8"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
@@ -3904,10 +3910,10 @@
       <c r="AV46" s="1"/>
     </row>
     <row r="47" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="3"/>
+      <c r="C47" s="4"/>
       <c r="E47" s="1" t="s">
         <v>32</v>
       </c>
@@ -3946,8 +3952,8 @@
       <c r="X47" s="1"/>
     </row>
     <row r="48" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="4"/>
-      <c r="C48" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="6"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
@@ -3982,8 +3988,8 @@
       <c r="X48" s="1"/>
     </row>
     <row r="49" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B49" s="4"/>
-      <c r="C49" s="5"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="6"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
@@ -4016,10 +4022,10 @@
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
       <c r="X49" s="1"/>
-      <c r="Z49" s="2" t="s">
+      <c r="Z49" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AA49" s="3"/>
+      <c r="AA49" s="4"/>
       <c r="AC49" s="1" t="s">
         <v>32</v>
       </c>
@@ -4058,8 +4064,8 @@
       <c r="AV49" s="1"/>
     </row>
     <row r="50" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="6"/>
-      <c r="C50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="8"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1" t="s">
@@ -4092,8 +4098,8 @@
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="5"/>
+      <c r="Z50" s="5"/>
+      <c r="AA50" s="6"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
       <c r="AE50" s="1" t="s">
@@ -4142,8 +4148,8 @@
       <c r="AV50" s="1"/>
     </row>
     <row r="51" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="5"/>
+      <c r="Z51" s="5"/>
+      <c r="AA51" s="6"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
       <c r="AE51" s="1" t="s">
@@ -4190,10 +4196,10 @@
       <c r="AV51" s="1"/>
     </row>
     <row r="52" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="3"/>
+      <c r="C52" s="4"/>
       <c r="E52" s="1" t="s">
         <v>32</v>
       </c>
@@ -4228,8 +4234,8 @@
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
-      <c r="Z52" s="6"/>
-      <c r="AA52" s="7"/>
+      <c r="Z52" s="7"/>
+      <c r="AA52" s="8"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
       <c r="AE52" s="1" t="s">
@@ -4276,8 +4282,8 @@
       <c r="AV52" s="1"/>
     </row>
     <row r="53" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B53" s="4"/>
-      <c r="C53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="6"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -4300,8 +4306,8 @@
       <c r="X53" s="1"/>
     </row>
     <row r="54" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B54" s="4"/>
-      <c r="C54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="6"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -4324,8 +4330,8 @@
       <c r="X54" s="1"/>
     </row>
     <row r="55" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="6"/>
-      <c r="C55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -4349,10 +4355,10 @@
     </row>
     <row r="56" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="57" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C57" s="3"/>
+      <c r="C57" s="4"/>
       <c r="E57" s="1" t="s">
         <v>32</v>
       </c>
@@ -4389,10 +4395,10 @@
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
-      <c r="Z57" s="2" t="s">
+      <c r="Z57" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AA57" s="3"/>
+      <c r="AA57" s="4"/>
       <c r="AC57" s="1" t="s">
         <v>32</v>
       </c>
@@ -4431,8 +4437,8 @@
       <c r="AV57" s="1"/>
     </row>
     <row r="58" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B58" s="4"/>
-      <c r="C58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="6"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
@@ -4471,8 +4477,8 @@
       </c>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
-      <c r="Z58" s="4"/>
-      <c r="AA58" s="5"/>
+      <c r="Z58" s="5"/>
+      <c r="AA58" s="6"/>
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
       <c r="AE58" s="1" t="s">
@@ -4511,8 +4517,8 @@
       <c r="AV58" s="1"/>
     </row>
     <row r="59" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B59" s="4"/>
-      <c r="C59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
@@ -4551,8 +4557,8 @@
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
-      <c r="Z59" s="4"/>
-      <c r="AA59" s="5"/>
+      <c r="Z59" s="5"/>
+      <c r="AA59" s="6"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
       <c r="AE59" s="1" t="s">
@@ -4591,8 +4597,8 @@
       <c r="AV59" s="1"/>
     </row>
     <row r="60" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="6"/>
-      <c r="C60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="8"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
@@ -4633,8 +4639,8 @@
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
-      <c r="Z60" s="6"/>
-      <c r="AA60" s="7"/>
+      <c r="Z60" s="7"/>
+      <c r="AA60" s="8"/>
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1" t="s">
@@ -4674,10 +4680,10 @@
     </row>
     <row r="61" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C62" s="3"/>
+      <c r="C62" s="4"/>
       <c r="E62" s="1" t="s">
         <v>32</v>
       </c>
@@ -4714,10 +4720,10 @@
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
-      <c r="Z62" s="2" t="s">
+      <c r="Z62" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AA62" s="3"/>
+      <c r="AA62" s="4"/>
       <c r="AC62" s="1" t="s">
         <v>32</v>
       </c>
@@ -4758,8 +4764,8 @@
       <c r="AV62" s="1"/>
     </row>
     <row r="63" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B63" s="4"/>
-      <c r="C63" s="5"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="6"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1" t="s">
@@ -4806,8 +4812,8 @@
       </c>
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
-      <c r="Z63" s="4"/>
-      <c r="AA63" s="5"/>
+      <c r="Z63" s="5"/>
+      <c r="AA63" s="6"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
       <c r="AE63" s="1" t="s">
@@ -4846,8 +4852,8 @@
       <c r="AV63" s="1"/>
     </row>
     <row r="64" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B64" s="4"/>
-      <c r="C64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="6"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
@@ -4892,8 +4898,8 @@
       </c>
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>
-      <c r="Z64" s="4"/>
-      <c r="AA64" s="5"/>
+      <c r="Z64" s="5"/>
+      <c r="AA64" s="6"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
       <c r="AE64" s="1" t="s">
@@ -4932,8 +4938,8 @@
       <c r="AV64" s="1"/>
     </row>
     <row r="65" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="6"/>
-      <c r="C65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -4954,8 +4960,8 @@
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
-      <c r="Z65" s="6"/>
-      <c r="AA65" s="7"/>
+      <c r="Z65" s="7"/>
+      <c r="AA65" s="8"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1"/>
@@ -4979,10 +4985,10 @@
     </row>
     <row r="67" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C68" s="3"/>
+      <c r="C68" s="4"/>
       <c r="E68" s="1" t="s">
         <v>32</v>
       </c>
@@ -5021,8 +5027,8 @@
       <c r="X68" s="1"/>
     </row>
     <row r="69" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B69" s="4"/>
-      <c r="C69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="6"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1" t="s">
@@ -5071,10 +5077,10 @@
       </c>
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
-      <c r="Z69" s="2" t="s">
+      <c r="Z69" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AA69" s="3"/>
+      <c r="AA69" s="4"/>
       <c r="AC69" s="1" t="s">
         <v>32</v>
       </c>
@@ -5113,8 +5119,8 @@
       <c r="AV69" s="1"/>
     </row>
     <row r="70" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B70" s="4"/>
-      <c r="C70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="6"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1" t="s">
@@ -5163,8 +5169,8 @@
       </c>
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
-      <c r="Z70" s="4"/>
-      <c r="AA70" s="5"/>
+      <c r="Z70" s="5"/>
+      <c r="AA70" s="6"/>
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
       <c r="AE70" s="1" t="s">
@@ -5213,8 +5219,8 @@
       <c r="AV70" s="1"/>
     </row>
     <row r="71" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="6"/>
-      <c r="C71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="8"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1" t="s">
@@ -5263,8 +5269,8 @@
       </c>
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
-      <c r="Z71" s="4"/>
-      <c r="AA71" s="5"/>
+      <c r="Z71" s="5"/>
+      <c r="AA71" s="6"/>
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
       <c r="AE71" s="1" t="s">
@@ -5317,8 +5323,8 @@
       <c r="AV71" s="1"/>
     </row>
     <row r="72" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z72" s="6"/>
-      <c r="AA72" s="7"/>
+      <c r="Z72" s="7"/>
+      <c r="AA72" s="8"/>
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
       <c r="AE72" s="1"/>
@@ -5341,10 +5347,10 @@
       <c r="AV72" s="1"/>
     </row>
     <row r="73" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C73" s="3"/>
+      <c r="C73" s="4"/>
       <c r="E73" s="1" t="s">
         <v>32</v>
       </c>
@@ -5397,8 +5403,8 @@
       <c r="X73" s="1"/>
     </row>
     <row r="74" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B74" s="4"/>
-      <c r="C74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="6"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -5419,10 +5425,10 @@
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
-      <c r="Z74" s="2" t="s">
+      <c r="Z74" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AA74" s="3"/>
+      <c r="AA74" s="4"/>
       <c r="AC74" s="1" t="s">
         <v>32</v>
       </c>
@@ -5461,8 +5467,8 @@
       <c r="AV74" s="1"/>
     </row>
     <row r="75" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B75" s="4"/>
-      <c r="C75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="6"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -5483,8 +5489,8 @@
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
-      <c r="Z75" s="4"/>
-      <c r="AA75" s="5"/>
+      <c r="Z75" s="5"/>
+      <c r="AA75" s="6"/>
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
       <c r="AE75" s="1" t="s">
@@ -5525,8 +5531,8 @@
       <c r="AV75" s="1"/>
     </row>
     <row r="76" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="6"/>
-      <c r="C76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="8"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -5547,8 +5553,8 @@
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
-      <c r="Z76" s="4"/>
-      <c r="AA76" s="5"/>
+      <c r="Z76" s="5"/>
+      <c r="AA76" s="6"/>
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
       <c r="AE76" s="1"/>
@@ -5571,8 +5577,8 @@
       <c r="AV76" s="1"/>
     </row>
     <row r="77" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z77" s="6"/>
-      <c r="AA77" s="7"/>
+      <c r="Z77" s="7"/>
+      <c r="AA77" s="8"/>
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
       <c r="AE77" s="1"/>
@@ -5596,10 +5602,10 @@
     </row>
     <row r="78" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="79" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z79" s="2" t="s">
+      <c r="Z79" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AA79" s="3"/>
+      <c r="AA79" s="4"/>
       <c r="AC79" s="1" t="s">
         <v>32</v>
       </c>
@@ -5638,10 +5644,10 @@
       <c r="AV79" s="1"/>
     </row>
     <row r="80" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C80" s="3"/>
+      <c r="C80" s="4"/>
       <c r="E80" s="1" t="s">
         <v>32</v>
       </c>
@@ -5680,8 +5686,8 @@
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
       <c r="X80" s="1"/>
-      <c r="Z80" s="4"/>
-      <c r="AA80" s="5"/>
+      <c r="Z80" s="5"/>
+      <c r="AA80" s="6"/>
       <c r="AC80" s="1"/>
       <c r="AD80" s="1"/>
       <c r="AE80" s="1" t="s">
@@ -5738,8 +5744,8 @@
       </c>
     </row>
     <row r="81" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B81" s="4"/>
-      <c r="C81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="6"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
@@ -5780,8 +5786,8 @@
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
       <c r="X81" s="1"/>
-      <c r="Z81" s="4"/>
-      <c r="AA81" s="5"/>
+      <c r="Z81" s="5"/>
+      <c r="AA81" s="6"/>
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
       <c r="AE81" s="1" t="s">
@@ -5830,8 +5836,8 @@
       <c r="AV81" s="1"/>
     </row>
     <row r="82" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="4"/>
-      <c r="C82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="6"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
@@ -5872,8 +5878,8 @@
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
       <c r="X82" s="1"/>
-      <c r="Z82" s="6"/>
-      <c r="AA82" s="7"/>
+      <c r="Z82" s="7"/>
+      <c r="AA82" s="8"/>
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
       <c r="AE82" s="1" t="s">
@@ -5918,8 +5924,8 @@
       <c r="AV82" s="1"/>
     </row>
     <row r="83" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="6"/>
-      <c r="C83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="8"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
@@ -5963,10 +5969,10 @@
     </row>
     <row r="85" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="86" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C86" s="3"/>
+      <c r="C86" s="4"/>
       <c r="E86" s="1" t="s">
         <v>32</v>
       </c>
@@ -6011,10 +6017,10 @@
       </c>
       <c r="W86" s="1"/>
       <c r="X86" s="1"/>
-      <c r="Z86" s="2" t="s">
+      <c r="Z86" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AA86" s="3"/>
+      <c r="AA86" s="4"/>
       <c r="AC86" s="1" t="s">
         <v>32</v>
       </c>
@@ -6067,8 +6073,8 @@
       <c r="AV86" s="1"/>
     </row>
     <row r="87" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B87" s="4"/>
-      <c r="C87" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="6"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
@@ -6109,8 +6115,8 @@
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
       <c r="X87" s="1"/>
-      <c r="Z87" s="4"/>
-      <c r="AA87" s="5"/>
+      <c r="Z87" s="5"/>
+      <c r="AA87" s="6"/>
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
       <c r="AE87" s="1" t="s">
@@ -6163,8 +6169,8 @@
       <c r="AV87" s="1"/>
     </row>
     <row r="88" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B88" s="4"/>
-      <c r="C88" s="5"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="6"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
@@ -6207,8 +6213,8 @@
       </c>
       <c r="W88" s="1"/>
       <c r="X88" s="1"/>
-      <c r="Z88" s="4"/>
-      <c r="AA88" s="5"/>
+      <c r="Z88" s="5"/>
+      <c r="AA88" s="6"/>
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
       <c r="AE88" s="1"/>
@@ -6231,8 +6237,8 @@
       <c r="AV88" s="1"/>
     </row>
     <row r="89" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="6"/>
-      <c r="C89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="8"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1" t="s">
@@ -6273,8 +6279,8 @@
       </c>
       <c r="W89" s="1"/>
       <c r="X89" s="1"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="7"/>
+      <c r="Z89" s="7"/>
+      <c r="AA89" s="8"/>
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
       <c r="AE89" s="1"/>
@@ -6298,10 +6304,10 @@
     </row>
     <row r="95" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C96" s="3"/>
+      <c r="C96" s="4"/>
       <c r="E96" s="1" t="s">
         <v>32</v>
       </c>
@@ -6352,8 +6358,8 @@
       <c r="X96" s="1"/>
     </row>
     <row r="97" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B97" s="4"/>
-      <c r="C97" s="5"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="6"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1" t="s">
@@ -6398,8 +6404,8 @@
       <c r="X97" s="1"/>
     </row>
     <row r="98" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B98" s="4"/>
-      <c r="C98" s="5"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="6"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
@@ -6422,8 +6428,8 @@
       <c r="X98" s="1"/>
     </row>
     <row r="99" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="6"/>
-      <c r="C99" s="7"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="8"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
@@ -6447,10 +6453,10 @@
     </row>
     <row r="101" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="102" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C102" s="9"/>
+      <c r="C102" s="10"/>
       <c r="E102" s="1" t="s">
         <v>32</v>
       </c>
@@ -6501,8 +6507,8 @@
       <c r="X102" s="1"/>
     </row>
     <row r="103" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B103" s="10"/>
-      <c r="C103" s="11"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="12"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1" t="s">
@@ -6551,8 +6557,8 @@
       <c r="X103" s="1"/>
     </row>
     <row r="104" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B104" s="10"/>
-      <c r="C104" s="11"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="12"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1" t="s">
@@ -6597,8 +6603,8 @@
       <c r="X104" s="1"/>
     </row>
     <row r="105" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="12"/>
-      <c r="C105" s="13"/>
+      <c r="B105" s="13"/>
+      <c r="C105" s="14"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
@@ -6622,10 +6628,10 @@
     </row>
     <row r="107" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B108" s="8" t="s">
+      <c r="B108" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C108" s="9"/>
+      <c r="C108" s="10"/>
       <c r="E108" s="1" t="s">
         <v>32</v>
       </c>
@@ -6676,8 +6682,8 @@
       <c r="X108" s="1"/>
     </row>
     <row r="109" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B109" s="10"/>
-      <c r="C109" s="11"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="12"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
       <c r="G109" s="1" t="s">
@@ -6718,8 +6724,8 @@
       <c r="X109" s="1"/>
     </row>
     <row r="110" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B110" s="10"/>
-      <c r="C110" s="11"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="12"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
       <c r="G110" s="1" t="s">
@@ -6754,8 +6760,8 @@
       <c r="X110" s="1"/>
     </row>
     <row r="111" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="12"/>
-      <c r="C111" s="13"/>
+      <c r="B111" s="13"/>
+      <c r="C111" s="14"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
@@ -6807,10 +6813,10 @@
     </row>
     <row r="113" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="114" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B114" s="8" t="s">
+      <c r="B114" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C114" s="9"/>
+      <c r="C114" s="10"/>
       <c r="E114" s="1" t="s">
         <v>32</v>
       </c>
@@ -6861,8 +6867,8 @@
       <c r="X114" s="1"/>
     </row>
     <row r="115" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B115" s="10"/>
-      <c r="C115" s="11"/>
+      <c r="B115" s="11"/>
+      <c r="C115" s="12"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
       <c r="G115" s="1" t="s">
@@ -6903,8 +6909,8 @@
       <c r="X115" s="1"/>
     </row>
     <row r="116" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B116" s="10"/>
-      <c r="C116" s="11"/>
+      <c r="B116" s="11"/>
+      <c r="C116" s="12"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
@@ -6939,8 +6945,8 @@
       <c r="X116" s="1"/>
     </row>
     <row r="117" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="12"/>
-      <c r="C117" s="13"/>
+      <c r="B117" s="13"/>
+      <c r="C117" s="14"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1" t="s">
@@ -6990,10 +6996,10 @@
     </row>
     <row r="119" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C120" s="3"/>
+      <c r="C120" s="4"/>
       <c r="E120" s="1" t="s">
         <v>32</v>
       </c>
@@ -7032,8 +7038,8 @@
       <c r="X120" s="1"/>
     </row>
     <row r="121" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B121" s="4"/>
-      <c r="C121" s="5"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="6"/>
       <c r="E121" s="1" t="s">
         <v>11</v>
       </c>
@@ -7043,7 +7049,7 @@
       <c r="G121" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H121" s="14" t="s">
+      <c r="H121" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I121" s="1"/>
@@ -7082,8 +7088,8 @@
       <c r="X121" s="1"/>
     </row>
     <row r="122" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B122" s="4"/>
-      <c r="C122" s="5"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="6"/>
       <c r="E122" s="1" t="s">
         <v>2</v>
       </c>
@@ -7120,8 +7126,8 @@
       <c r="X122" s="1"/>
     </row>
     <row r="123" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="6"/>
-      <c r="C123" s="7"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="8"/>
       <c r="E123" s="1" t="s">
         <v>6</v>
       </c>
@@ -7179,6 +7185,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B114:C117"/>
+    <mergeCell ref="Z86:AA89"/>
+    <mergeCell ref="B86:C89"/>
+    <mergeCell ref="B80:C83"/>
+    <mergeCell ref="B73:C76"/>
+    <mergeCell ref="B68:C71"/>
+    <mergeCell ref="B96:C99"/>
+    <mergeCell ref="B108:C111"/>
+    <mergeCell ref="B102:C105"/>
+    <mergeCell ref="Z79:AA82"/>
+    <mergeCell ref="Z74:AA77"/>
+    <mergeCell ref="Z57:AA60"/>
+    <mergeCell ref="Z62:AA65"/>
+    <mergeCell ref="Z69:AA72"/>
     <mergeCell ref="B120:C123"/>
     <mergeCell ref="B4:C7"/>
     <mergeCell ref="B9:C12"/>
@@ -7195,20 +7215,6 @@
     <mergeCell ref="Z32:AA35"/>
     <mergeCell ref="Z37:AA40"/>
     <mergeCell ref="Z43:AA46"/>
-    <mergeCell ref="Z79:AA82"/>
-    <mergeCell ref="Z74:AA77"/>
-    <mergeCell ref="Z57:AA60"/>
-    <mergeCell ref="Z62:AA65"/>
-    <mergeCell ref="Z69:AA72"/>
-    <mergeCell ref="B80:C83"/>
-    <mergeCell ref="B73:C76"/>
-    <mergeCell ref="B68:C71"/>
-    <mergeCell ref="B96:C99"/>
-    <mergeCell ref="B108:C111"/>
-    <mergeCell ref="B102:C105"/>
-    <mergeCell ref="B114:C117"/>
-    <mergeCell ref="Z86:AA89"/>
-    <mergeCell ref="B86:C89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -7229,10 +7235,10 @@
   <sheetData>
     <row r="16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="DE17" s="2" t="s">
+      <c r="DE17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="DF17" s="3"/>
+      <c r="DF17" s="4"/>
       <c r="DH17" s="1" t="s">
         <v>32</v>
       </c>
@@ -7283,8 +7289,8 @@
       <c r="EA17" s="1"/>
     </row>
     <row r="18" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE18" s="4"/>
-      <c r="DF18" s="5"/>
+      <c r="DE18" s="5"/>
+      <c r="DF18" s="6"/>
       <c r="DH18" s="1"/>
       <c r="DI18" s="1"/>
       <c r="DJ18" s="1" t="s">
@@ -7329,10 +7335,10 @@
       <c r="EA18" s="1"/>
     </row>
     <row r="19" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD19" s="2" t="s">
+      <c r="CD19" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="CE19" s="3"/>
+      <c r="CE19" s="4"/>
       <c r="CG19" s="1" t="s">
         <v>32</v>
       </c>
@@ -7369,8 +7375,8 @@
       <c r="CX19" s="1"/>
       <c r="CY19" s="1"/>
       <c r="CZ19" s="1"/>
-      <c r="DE19" s="4"/>
-      <c r="DF19" s="5"/>
+      <c r="DE19" s="5"/>
+      <c r="DF19" s="6"/>
       <c r="DH19" s="1"/>
       <c r="DI19" s="1"/>
       <c r="DJ19" s="1"/>
@@ -7393,8 +7399,8 @@
       <c r="EA19" s="1"/>
     </row>
     <row r="20" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD20" s="4"/>
-      <c r="CE20" s="5"/>
+      <c r="CD20" s="5"/>
+      <c r="CE20" s="6"/>
       <c r="CG20" s="1" t="s">
         <v>11</v>
       </c>
@@ -7404,7 +7410,7 @@
       <c r="CI20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="CJ20" s="14" t="s">
+      <c r="CJ20" s="2" t="s">
         <v>4</v>
       </c>
       <c r="CK20" s="1"/>
@@ -7441,8 +7447,8 @@
       <c r="CX20" s="1"/>
       <c r="CY20" s="1"/>
       <c r="CZ20" s="1"/>
-      <c r="DE20" s="6"/>
-      <c r="DF20" s="7"/>
+      <c r="DE20" s="7"/>
+      <c r="DF20" s="8"/>
       <c r="DH20" s="1"/>
       <c r="DI20" s="1"/>
       <c r="DJ20" s="1"/>
@@ -7465,8 +7471,8 @@
       <c r="EA20" s="1"/>
     </row>
     <row r="21" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD21" s="4"/>
-      <c r="CE21" s="5"/>
+      <c r="CD21" s="5"/>
+      <c r="CE21" s="6"/>
       <c r="CG21" s="1" t="s">
         <v>2</v>
       </c>
@@ -7503,8 +7509,8 @@
       <c r="CZ21" s="1"/>
     </row>
     <row r="22" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD22" s="6"/>
-      <c r="CE22" s="7"/>
+      <c r="CD22" s="7"/>
+      <c r="CE22" s="8"/>
       <c r="CG22" s="1" t="s">
         <v>6</v>
       </c>
@@ -7561,10 +7567,10 @@
       <c r="CZ22" s="1"/>
     </row>
     <row r="23" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="DE23" s="8" t="s">
+      <c r="DE23" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="DF23" s="9"/>
+      <c r="DF23" s="10"/>
       <c r="DH23" s="1" t="s">
         <v>32</v>
       </c>
@@ -7615,8 +7621,8 @@
       <c r="EA23" s="1"/>
     </row>
     <row r="24" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="DE24" s="10"/>
-      <c r="DF24" s="11"/>
+      <c r="DE24" s="11"/>
+      <c r="DF24" s="12"/>
       <c r="DH24" s="1"/>
       <c r="DI24" s="1"/>
       <c r="DJ24" s="1" t="s">
@@ -7665,8 +7671,8 @@
       <c r="EA24" s="1"/>
     </row>
     <row r="25" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="DE25" s="10"/>
-      <c r="DF25" s="11"/>
+      <c r="DE25" s="11"/>
+      <c r="DF25" s="12"/>
       <c r="DH25" s="1"/>
       <c r="DI25" s="1"/>
       <c r="DJ25" s="1" t="s">
@@ -7711,8 +7717,8 @@
       <c r="EA25" s="1"/>
     </row>
     <row r="26" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE26" s="12"/>
-      <c r="DF26" s="13"/>
+      <c r="DE26" s="13"/>
+      <c r="DF26" s="14"/>
       <c r="DH26" s="1"/>
       <c r="DI26" s="1"/>
       <c r="DJ26" s="1"/>
@@ -7736,10 +7742,10 @@
     </row>
     <row r="27" spans="82:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD28" s="2" t="s">
+      <c r="CD28" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="CE28" s="3"/>
+      <c r="CE28" s="4"/>
       <c r="CG28" s="1" t="s">
         <v>32</v>
       </c>
@@ -7780,8 +7786,8 @@
       <c r="CZ28" s="1"/>
     </row>
     <row r="29" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD29" s="4"/>
-      <c r="CE29" s="5"/>
+      <c r="CD29" s="5"/>
+      <c r="CE29" s="6"/>
       <c r="CG29" s="1"/>
       <c r="CH29" s="1"/>
       <c r="CI29" s="1" t="s">
@@ -7822,10 +7828,10 @@
       <c r="CX29" s="1"/>
       <c r="CY29" s="1"/>
       <c r="CZ29" s="1"/>
-      <c r="DE29" s="8" t="s">
+      <c r="DE29" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="DF29" s="9"/>
+      <c r="DF29" s="10"/>
       <c r="DH29" s="1" t="s">
         <v>32</v>
       </c>
@@ -7876,8 +7882,8 @@
       <c r="EA29" s="1"/>
     </row>
     <row r="30" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD30" s="4"/>
-      <c r="CE30" s="5"/>
+      <c r="CD30" s="5"/>
+      <c r="CE30" s="6"/>
       <c r="CG30" s="1"/>
       <c r="CH30" s="1"/>
       <c r="CI30" s="1" t="s">
@@ -7918,8 +7924,8 @@
       <c r="CX30" s="1"/>
       <c r="CY30" s="1"/>
       <c r="CZ30" s="1"/>
-      <c r="DE30" s="10"/>
-      <c r="DF30" s="11"/>
+      <c r="DE30" s="11"/>
+      <c r="DF30" s="12"/>
       <c r="DH30" s="1"/>
       <c r="DI30" s="1"/>
       <c r="DJ30" s="1" t="s">
@@ -7960,8 +7966,8 @@
       <c r="EA30" s="1"/>
     </row>
     <row r="31" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD31" s="6"/>
-      <c r="CE31" s="7"/>
+      <c r="CD31" s="7"/>
+      <c r="CE31" s="8"/>
       <c r="CG31" s="1"/>
       <c r="CH31" s="1"/>
       <c r="CI31" s="1" t="s">
@@ -8002,8 +8008,8 @@
       </c>
       <c r="CY31" s="1"/>
       <c r="CZ31" s="1"/>
-      <c r="DE31" s="10"/>
-      <c r="DF31" s="11"/>
+      <c r="DE31" s="11"/>
+      <c r="DF31" s="12"/>
       <c r="DH31" s="1"/>
       <c r="DI31" s="1"/>
       <c r="DJ31" s="1" t="s">
@@ -8038,8 +8044,8 @@
       <c r="EA31" s="1"/>
     </row>
     <row r="32" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE32" s="12"/>
-      <c r="DF32" s="13"/>
+      <c r="DE32" s="13"/>
+      <c r="DF32" s="14"/>
       <c r="DH32" s="1"/>
       <c r="DI32" s="1"/>
       <c r="DJ32" s="1" t="s">
@@ -8091,10 +8097,10 @@
     </row>
     <row r="33" spans="55:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC34" s="2" t="s">
+      <c r="BC34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="BD34" s="3"/>
+      <c r="BD34" s="4"/>
       <c r="BF34" s="1" t="s">
         <v>32</v>
       </c>
@@ -8131,10 +8137,10 @@
       <c r="BW34" s="1"/>
       <c r="BX34" s="1"/>
       <c r="BY34" s="1"/>
-      <c r="CD34" s="2" t="s">
+      <c r="CD34" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="CE34" s="3"/>
+      <c r="CE34" s="4"/>
       <c r="CG34" s="1" t="s">
         <v>32</v>
       </c>
@@ -8181,8 +8187,8 @@
       <c r="CZ34" s="1"/>
     </row>
     <row r="35" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC35" s="4"/>
-      <c r="BD35" s="5"/>
+      <c r="BC35" s="5"/>
+      <c r="BD35" s="6"/>
       <c r="BF35" s="1"/>
       <c r="BG35" s="1"/>
       <c r="BH35" s="1" t="s">
@@ -8233,8 +8239,8 @@
       </c>
       <c r="BX35" s="1"/>
       <c r="BY35" s="1"/>
-      <c r="CD35" s="4"/>
-      <c r="CE35" s="5"/>
+      <c r="CD35" s="5"/>
+      <c r="CE35" s="6"/>
       <c r="CG35" s="1"/>
       <c r="CH35" s="1"/>
       <c r="CI35" s="1" t="s">
@@ -8275,10 +8281,10 @@
       <c r="CX35" s="1"/>
       <c r="CY35" s="1"/>
       <c r="CZ35" s="1"/>
-      <c r="DE35" s="8" t="s">
+      <c r="DE35" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="DF35" s="9"/>
+      <c r="DF35" s="10"/>
       <c r="DH35" s="1" t="s">
         <v>32</v>
       </c>
@@ -8329,8 +8335,8 @@
       <c r="EA35" s="1"/>
     </row>
     <row r="36" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC36" s="4"/>
-      <c r="BD36" s="5"/>
+      <c r="BC36" s="5"/>
+      <c r="BD36" s="6"/>
       <c r="BF36" s="1"/>
       <c r="BG36" s="1"/>
       <c r="BH36" s="1" t="s">
@@ -8367,8 +8373,8 @@
       <c r="BW36" s="1"/>
       <c r="BX36" s="1"/>
       <c r="BY36" s="1"/>
-      <c r="CD36" s="4"/>
-      <c r="CE36" s="5"/>
+      <c r="CD36" s="5"/>
+      <c r="CE36" s="6"/>
       <c r="CG36" s="1"/>
       <c r="CH36" s="1"/>
       <c r="CI36" s="1" t="s">
@@ -8411,8 +8417,8 @@
       </c>
       <c r="CY36" s="1"/>
       <c r="CZ36" s="1"/>
-      <c r="DE36" s="10"/>
-      <c r="DF36" s="11"/>
+      <c r="DE36" s="11"/>
+      <c r="DF36" s="12"/>
       <c r="DH36" s="1"/>
       <c r="DI36" s="1"/>
       <c r="DJ36" s="1" t="s">
@@ -8453,8 +8459,8 @@
       <c r="EA36" s="1"/>
     </row>
     <row r="37" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC37" s="6"/>
-      <c r="BD37" s="7"/>
+      <c r="BC37" s="7"/>
+      <c r="BD37" s="8"/>
       <c r="BF37" s="1"/>
       <c r="BG37" s="1"/>
       <c r="BH37" s="1" t="s">
@@ -8491,8 +8497,8 @@
       <c r="BW37" s="1"/>
       <c r="BX37" s="1"/>
       <c r="BY37" s="1"/>
-      <c r="CD37" s="6"/>
-      <c r="CE37" s="7"/>
+      <c r="CD37" s="7"/>
+      <c r="CE37" s="8"/>
       <c r="CG37" s="1"/>
       <c r="CH37" s="1"/>
       <c r="CI37" s="1" t="s">
@@ -8533,8 +8539,8 @@
       </c>
       <c r="CY37" s="1"/>
       <c r="CZ37" s="1"/>
-      <c r="DE37" s="10"/>
-      <c r="DF37" s="11"/>
+      <c r="DE37" s="11"/>
+      <c r="DF37" s="12"/>
       <c r="DH37" s="1"/>
       <c r="DI37" s="1"/>
       <c r="DJ37" s="1" t="s">
@@ -8569,8 +8575,8 @@
       <c r="EA37" s="1"/>
     </row>
     <row r="38" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE38" s="12"/>
-      <c r="DF38" s="13"/>
+      <c r="DE38" s="13"/>
+      <c r="DF38" s="14"/>
       <c r="DH38" s="1"/>
       <c r="DI38" s="1"/>
       <c r="DJ38" s="1" t="s">
@@ -8619,10 +8625,10 @@
       <c r="EA38" s="1"/>
     </row>
     <row r="39" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC39" s="2" t="s">
+      <c r="BC39" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="BD39" s="3"/>
+      <c r="BD39" s="4"/>
       <c r="BF39" s="1" t="s">
         <v>32</v>
       </c>
@@ -8663,8 +8669,8 @@
       <c r="BY39" s="1"/>
     </row>
     <row r="40" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC40" s="4"/>
-      <c r="BD40" s="5"/>
+      <c r="BC40" s="5"/>
+      <c r="BD40" s="6"/>
       <c r="BF40" s="1"/>
       <c r="BG40" s="1"/>
       <c r="BH40" s="1" t="s">
@@ -8703,8 +8709,8 @@
       <c r="BY40" s="1"/>
     </row>
     <row r="41" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC41" s="4"/>
-      <c r="BD41" s="5"/>
+      <c r="BC41" s="5"/>
+      <c r="BD41" s="6"/>
       <c r="BF41" s="1"/>
       <c r="BG41" s="1"/>
       <c r="BH41" s="1" t="s">
@@ -8743,8 +8749,8 @@
       <c r="BY41" s="1"/>
     </row>
     <row r="42" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC42" s="6"/>
-      <c r="BD42" s="7"/>
+      <c r="BC42" s="7"/>
+      <c r="BD42" s="8"/>
       <c r="BF42" s="1"/>
       <c r="BG42" s="1"/>
       <c r="BH42" s="1" t="s">
@@ -8784,10 +8790,10 @@
     </row>
     <row r="45" spans="55:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD46" s="2" t="s">
+      <c r="CD46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="CE46" s="3"/>
+      <c r="CE46" s="4"/>
       <c r="CG46" s="1" t="s">
         <v>32</v>
       </c>
@@ -8824,10 +8830,10 @@
       <c r="CX46" s="1"/>
       <c r="CY46" s="1"/>
       <c r="CZ46" s="1"/>
-      <c r="DE46" s="2" t="s">
+      <c r="DE46" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="DF46" s="3"/>
+      <c r="DF46" s="4"/>
       <c r="DH46" s="1" t="s">
         <v>32</v>
       </c>
@@ -8866,8 +8872,8 @@
       <c r="EA46" s="1"/>
     </row>
     <row r="47" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD47" s="4"/>
-      <c r="CE47" s="5"/>
+      <c r="CD47" s="5"/>
+      <c r="CE47" s="6"/>
       <c r="CG47" s="1"/>
       <c r="CH47" s="1"/>
       <c r="CI47" s="1" t="s">
@@ -8900,8 +8906,8 @@
       <c r="CX47" s="1"/>
       <c r="CY47" s="1"/>
       <c r="CZ47" s="1"/>
-      <c r="DE47" s="4"/>
-      <c r="DF47" s="5"/>
+      <c r="DE47" s="5"/>
+      <c r="DF47" s="6"/>
       <c r="DH47" s="1"/>
       <c r="DI47" s="1"/>
       <c r="DJ47" s="1" t="s">
@@ -8942,8 +8948,8 @@
       <c r="EA47" s="1"/>
     </row>
     <row r="48" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD48" s="4"/>
-      <c r="CE48" s="5"/>
+      <c r="CD48" s="5"/>
+      <c r="CE48" s="6"/>
       <c r="CG48" s="1"/>
       <c r="CH48" s="1"/>
       <c r="CI48" s="1" t="s">
@@ -8976,8 +8982,8 @@
       <c r="CX48" s="1"/>
       <c r="CY48" s="1"/>
       <c r="CZ48" s="1"/>
-      <c r="DE48" s="4"/>
-      <c r="DF48" s="5"/>
+      <c r="DE48" s="5"/>
+      <c r="DF48" s="6"/>
       <c r="DH48" s="1"/>
       <c r="DI48" s="1"/>
       <c r="DJ48" s="1" t="s">
@@ -9018,8 +9024,8 @@
       <c r="EA48" s="1"/>
     </row>
     <row r="49" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD49" s="6"/>
-      <c r="CE49" s="7"/>
+      <c r="CD49" s="7"/>
+      <c r="CE49" s="8"/>
       <c r="CG49" s="1"/>
       <c r="CH49" s="1"/>
       <c r="CI49" s="1" t="s">
@@ -9052,8 +9058,8 @@
       <c r="CX49" s="1"/>
       <c r="CY49" s="1"/>
       <c r="CZ49" s="1"/>
-      <c r="DE49" s="6"/>
-      <c r="DF49" s="7"/>
+      <c r="DE49" s="7"/>
+      <c r="DF49" s="8"/>
       <c r="DH49" s="1"/>
       <c r="DI49" s="1"/>
       <c r="DJ49" s="1" t="s">
@@ -9097,10 +9103,10 @@
     </row>
     <row r="50" spans="28:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="51" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD51" s="2" t="s">
+      <c r="CD51" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="CE51" s="3"/>
+      <c r="CE51" s="4"/>
       <c r="CG51" s="1" t="s">
         <v>32</v>
       </c>
@@ -9135,10 +9141,10 @@
       <c r="CX51" s="1"/>
       <c r="CY51" s="1"/>
       <c r="CZ51" s="1"/>
-      <c r="DE51" s="2" t="s">
+      <c r="DE51" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="DF51" s="3"/>
+      <c r="DF51" s="4"/>
       <c r="DH51" s="1" t="s">
         <v>32</v>
       </c>
@@ -9177,8 +9183,8 @@
       <c r="EA51" s="1"/>
     </row>
     <row r="52" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD52" s="4"/>
-      <c r="CE52" s="5"/>
+      <c r="CD52" s="5"/>
+      <c r="CE52" s="6"/>
       <c r="CG52" s="1"/>
       <c r="CH52" s="1"/>
       <c r="CI52" s="1"/>
@@ -9199,8 +9205,8 @@
       <c r="CX52" s="1"/>
       <c r="CY52" s="1"/>
       <c r="CZ52" s="1"/>
-      <c r="DE52" s="4"/>
-      <c r="DF52" s="5"/>
+      <c r="DE52" s="5"/>
+      <c r="DF52" s="6"/>
       <c r="DH52" s="1"/>
       <c r="DI52" s="1"/>
       <c r="DJ52" s="1" t="s">
@@ -9249,8 +9255,8 @@
       <c r="EA52" s="1"/>
     </row>
     <row r="53" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD53" s="4"/>
-      <c r="CE53" s="5"/>
+      <c r="CD53" s="5"/>
+      <c r="CE53" s="6"/>
       <c r="CG53" s="1"/>
       <c r="CH53" s="1"/>
       <c r="CI53" s="1"/>
@@ -9271,8 +9277,8 @@
       <c r="CX53" s="1"/>
       <c r="CY53" s="1"/>
       <c r="CZ53" s="1"/>
-      <c r="DE53" s="4"/>
-      <c r="DF53" s="5"/>
+      <c r="DE53" s="5"/>
+      <c r="DF53" s="6"/>
       <c r="DH53" s="1"/>
       <c r="DI53" s="1"/>
       <c r="DJ53" s="1" t="s">
@@ -9319,8 +9325,8 @@
       <c r="EA53" s="1"/>
     </row>
     <row r="54" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD54" s="6"/>
-      <c r="CE54" s="7"/>
+      <c r="CD54" s="7"/>
+      <c r="CE54" s="8"/>
       <c r="CG54" s="1"/>
       <c r="CH54" s="1"/>
       <c r="CI54" s="1"/>
@@ -9341,8 +9347,8 @@
       <c r="CX54" s="1"/>
       <c r="CY54" s="1"/>
       <c r="CZ54" s="1"/>
-      <c r="DE54" s="6"/>
-      <c r="DF54" s="7"/>
+      <c r="DE54" s="7"/>
+      <c r="DF54" s="8"/>
       <c r="DH54" s="1"/>
       <c r="DI54" s="1"/>
       <c r="DJ54" s="1"/>
@@ -9365,10 +9371,10 @@
       <c r="EA54" s="1"/>
     </row>
     <row r="55" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC55" s="2" t="s">
+      <c r="BC55" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="BD55" s="3"/>
+      <c r="BD55" s="4"/>
       <c r="BF55" s="1" t="s">
         <v>32</v>
       </c>
@@ -9407,8 +9413,8 @@
       <c r="BY55" s="1"/>
     </row>
     <row r="56" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC56" s="4"/>
-      <c r="BD56" s="5"/>
+      <c r="BC56" s="5"/>
+      <c r="BD56" s="6"/>
       <c r="BF56" s="1"/>
       <c r="BG56" s="1"/>
       <c r="BH56" s="1" t="s">
@@ -9447,8 +9453,8 @@
       <c r="BY56" s="1"/>
     </row>
     <row r="57" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC57" s="4"/>
-      <c r="BD57" s="5"/>
+      <c r="BC57" s="5"/>
+      <c r="BD57" s="6"/>
       <c r="BF57" s="1"/>
       <c r="BG57" s="1"/>
       <c r="BH57" s="1" t="s">
@@ -9493,19 +9499,35 @@
       <c r="BY57" s="1"/>
     </row>
     <row r="58" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC58" s="6"/>
-      <c r="BD58" s="7"/>
+      <c r="BC58" s="7"/>
+      <c r="BD58" s="8"/>
       <c r="BF58" s="1"/>
       <c r="BG58" s="1"/>
-      <c r="BH58" s="1"/>
-      <c r="BI58" s="1"/>
-      <c r="BJ58" s="1"/>
+      <c r="BH58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="BI58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ58" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BK58" s="1"/>
-      <c r="BL58" s="1"/>
-      <c r="BM58" s="1"/>
-      <c r="BN58" s="1"/>
-      <c r="BO58" s="1"/>
-      <c r="BP58" s="1"/>
+      <c r="BL58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="BM58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BN58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BO58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP58" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BQ58" s="1"/>
       <c r="BR58" s="1"/>
       <c r="BS58" s="1"/>
@@ -9517,10 +9539,10 @@
       <c r="BY58" s="1"/>
     </row>
     <row r="59" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD59" s="2" t="s">
+      <c r="CD59" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="CE59" s="3"/>
+      <c r="CE59" s="4"/>
       <c r="CG59" s="1" t="s">
         <v>32</v>
       </c>
@@ -9559,8 +9581,8 @@
       <c r="CZ59" s="1"/>
     </row>
     <row r="60" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD60" s="4"/>
-      <c r="CE60" s="5"/>
+      <c r="CD60" s="5"/>
+      <c r="CE60" s="6"/>
       <c r="CG60" s="1"/>
       <c r="CH60" s="1"/>
       <c r="CI60" s="1" t="s">
@@ -9611,8 +9633,8 @@
       <c r="CZ60" s="1"/>
     </row>
     <row r="61" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD61" s="4"/>
-      <c r="CE61" s="5"/>
+      <c r="CD61" s="5"/>
+      <c r="CE61" s="6"/>
       <c r="CG61" s="1"/>
       <c r="CH61" s="1"/>
       <c r="CI61" s="1" t="s">
@@ -9663,8 +9685,8 @@
       <c r="CZ61" s="1"/>
     </row>
     <row r="62" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD62" s="6"/>
-      <c r="CE62" s="7"/>
+      <c r="CD62" s="7"/>
+      <c r="CE62" s="8"/>
       <c r="CG62" s="1"/>
       <c r="CH62" s="1"/>
       <c r="CI62" s="1" t="s">
@@ -9716,10 +9738,10 @@
     </row>
     <row r="63" spans="28:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="AB64" s="2" t="s">
+      <c r="AB64" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AC64" s="3"/>
+      <c r="AC64" s="4"/>
       <c r="AE64" s="1" t="s">
         <v>32</v>
       </c>
@@ -9760,10 +9782,10 @@
       <c r="AV64" s="1"/>
       <c r="AW64" s="1"/>
       <c r="AX64" s="1"/>
-      <c r="CD64" s="2" t="s">
+      <c r="CD64" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="CE64" s="3"/>
+      <c r="CE64" s="4"/>
       <c r="CG64" s="1" t="s">
         <v>32</v>
       </c>
@@ -9816,8 +9838,8 @@
       <c r="CZ64" s="1"/>
     </row>
     <row r="65" spans="2:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="AB65" s="4"/>
-      <c r="AC65" s="5"/>
+      <c r="AB65" s="5"/>
+      <c r="AC65" s="6"/>
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
       <c r="AG65" s="1" t="s">
@@ -9850,8 +9872,8 @@
       <c r="AV65" s="1"/>
       <c r="AW65" s="1"/>
       <c r="AX65" s="1"/>
-      <c r="CD65" s="4"/>
-      <c r="CE65" s="5"/>
+      <c r="CD65" s="5"/>
+      <c r="CE65" s="6"/>
       <c r="CG65" s="1"/>
       <c r="CH65" s="1"/>
       <c r="CI65" s="1"/>
@@ -9874,8 +9896,8 @@
       <c r="CZ65" s="1"/>
     </row>
     <row r="66" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AB66" s="4"/>
-      <c r="AC66" s="5"/>
+      <c r="AB66" s="5"/>
+      <c r="AC66" s="6"/>
       <c r="AE66" s="1"/>
       <c r="AF66" s="1"/>
       <c r="AG66" s="1" t="s">
@@ -9910,8 +9932,8 @@
       <c r="AV66" s="1"/>
       <c r="AW66" s="1"/>
       <c r="AX66" s="1"/>
-      <c r="CD66" s="4"/>
-      <c r="CE66" s="5"/>
+      <c r="CD66" s="5"/>
+      <c r="CE66" s="6"/>
       <c r="CG66" s="1"/>
       <c r="CH66" s="1"/>
       <c r="CI66" s="1"/>
@@ -9934,10 +9956,10 @@
       <c r="CZ66" s="1"/>
     </row>
     <row r="67" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C67" s="3"/>
+      <c r="C67" s="4"/>
       <c r="E67" s="1" t="s">
         <v>0</v>
       </c>
@@ -9976,8 +9998,8 @@
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
       <c r="X67" s="1"/>
-      <c r="AB67" s="6"/>
-      <c r="AC67" s="7"/>
+      <c r="AB67" s="7"/>
+      <c r="AC67" s="8"/>
       <c r="AE67" s="1"/>
       <c r="AF67" s="1"/>
       <c r="AG67" s="1" t="s">
@@ -10012,8 +10034,8 @@
       <c r="AV67" s="1"/>
       <c r="AW67" s="1"/>
       <c r="AX67" s="1"/>
-      <c r="CD67" s="6"/>
-      <c r="CE67" s="7"/>
+      <c r="CD67" s="7"/>
+      <c r="CE67" s="8"/>
       <c r="CG67" s="1"/>
       <c r="CH67" s="1"/>
       <c r="CI67" s="1"/>
@@ -10036,8 +10058,8 @@
       <c r="CZ67" s="1"/>
     </row>
     <row r="68" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="4"/>
-      <c r="C68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="6"/>
       <c r="E68" s="1" t="s">
         <v>3</v>
       </c>
@@ -10078,10 +10100,10 @@
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
-      <c r="BC68" s="2" t="s">
+      <c r="BC68" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="BD68" s="3"/>
+      <c r="BD68" s="4"/>
       <c r="BF68" s="1" t="s">
         <v>32</v>
       </c>
@@ -10120,8 +10142,8 @@
       <c r="BY68" s="1"/>
     </row>
     <row r="69" spans="2:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B69" s="4"/>
-      <c r="C69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="6"/>
       <c r="E69" s="1" t="s">
         <v>4</v>
       </c>
@@ -10156,10 +10178,10 @@
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
-      <c r="AB69" s="2" t="s">
+      <c r="AB69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AC69" s="3"/>
+      <c r="AC69" s="4"/>
       <c r="AE69" s="1" t="s">
         <v>32</v>
       </c>
@@ -10206,8 +10228,8 @@
       <c r="AV69" s="1"/>
       <c r="AW69" s="1"/>
       <c r="AX69" s="1"/>
-      <c r="BC69" s="4"/>
-      <c r="BD69" s="5"/>
+      <c r="BC69" s="5"/>
+      <c r="BD69" s="6"/>
       <c r="BF69" s="1"/>
       <c r="BG69" s="1"/>
       <c r="BH69" s="1" t="s">
@@ -10244,8 +10266,8 @@
       <c r="BY69" s="1"/>
     </row>
     <row r="70" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="6"/>
-      <c r="C70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="8"/>
       <c r="E70" s="1" t="s">
         <v>13</v>
       </c>
@@ -10286,8 +10308,8 @@
         <v>1</v>
       </c>
       <c r="X70" s="1"/>
-      <c r="AB70" s="4"/>
-      <c r="AC70" s="5"/>
+      <c r="AB70" s="5"/>
+      <c r="AC70" s="6"/>
       <c r="AE70" s="1"/>
       <c r="AF70" s="1"/>
       <c r="AG70" s="1" t="s">
@@ -10324,8 +10346,8 @@
       <c r="AV70" s="1"/>
       <c r="AW70" s="1"/>
       <c r="AX70" s="1"/>
-      <c r="BC70" s="4"/>
-      <c r="BD70" s="5"/>
+      <c r="BC70" s="5"/>
+      <c r="BD70" s="6"/>
       <c r="BF70" s="1"/>
       <c r="BG70" s="1"/>
       <c r="BH70" s="1" t="s">
@@ -10362,8 +10384,8 @@
       <c r="BY70" s="1"/>
     </row>
     <row r="71" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AB71" s="4"/>
-      <c r="AC71" s="5"/>
+      <c r="AB71" s="5"/>
+      <c r="AC71" s="6"/>
       <c r="AE71" s="1"/>
       <c r="AF71" s="1"/>
       <c r="AG71" s="1" t="s">
@@ -10400,8 +10422,8 @@
       <c r="AV71" s="1"/>
       <c r="AW71" s="1"/>
       <c r="AX71" s="1"/>
-      <c r="BC71" s="6"/>
-      <c r="BD71" s="7"/>
+      <c r="BC71" s="7"/>
+      <c r="BD71" s="8"/>
       <c r="BF71" s="1"/>
       <c r="BG71" s="1"/>
       <c r="BH71" s="1"/>
@@ -10422,10 +10444,10 @@
       <c r="BW71" s="1"/>
       <c r="BX71" s="1"/>
       <c r="BY71" s="1"/>
-      <c r="CD71" s="2" t="s">
+      <c r="CD71" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="CE71" s="3"/>
+      <c r="CE71" s="4"/>
       <c r="CG71" s="1" t="s">
         <v>32</v>
       </c>
@@ -10464,8 +10486,8 @@
       <c r="CZ71" s="1"/>
     </row>
     <row r="72" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AB72" s="6"/>
-      <c r="AC72" s="7"/>
+      <c r="AB72" s="7"/>
+      <c r="AC72" s="8"/>
       <c r="AE72" s="1"/>
       <c r="AF72" s="1"/>
       <c r="AG72" s="1" t="s">
@@ -10494,8 +10516,8 @@
       <c r="AV72" s="1"/>
       <c r="AW72" s="1"/>
       <c r="AX72" s="1"/>
-      <c r="CD72" s="4"/>
-      <c r="CE72" s="5"/>
+      <c r="CD72" s="5"/>
+      <c r="CE72" s="6"/>
       <c r="CG72" s="1"/>
       <c r="CH72" s="1"/>
       <c r="CI72" s="1" t="s">
@@ -10536,8 +10558,8 @@
       <c r="CZ72" s="1"/>
     </row>
     <row r="73" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD73" s="4"/>
-      <c r="CE73" s="5"/>
+      <c r="CD73" s="5"/>
+      <c r="CE73" s="6"/>
       <c r="CG73" s="1"/>
       <c r="CH73" s="1"/>
       <c r="CI73" s="1" t="s">
@@ -10588,10 +10610,10 @@
       <c r="CZ73" s="1"/>
     </row>
     <row r="74" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC74" s="2" t="s">
+      <c r="BC74" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="BD74" s="3"/>
+      <c r="BD74" s="4"/>
       <c r="BF74" s="1" t="s">
         <v>32</v>
       </c>
@@ -10628,8 +10650,8 @@
       <c r="BW74" s="1"/>
       <c r="BX74" s="1"/>
       <c r="BY74" s="1"/>
-      <c r="CD74" s="6"/>
-      <c r="CE74" s="7"/>
+      <c r="CD74" s="7"/>
+      <c r="CE74" s="8"/>
       <c r="CG74" s="1"/>
       <c r="CH74" s="1"/>
       <c r="CI74" s="1" t="s">
@@ -10670,8 +10692,8 @@
       <c r="CZ74" s="1"/>
     </row>
     <row r="75" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC75" s="4"/>
-      <c r="BD75" s="5"/>
+      <c r="BC75" s="5"/>
+      <c r="BD75" s="6"/>
       <c r="BF75" s="1"/>
       <c r="BG75" s="1"/>
       <c r="BH75" s="1" t="s">
@@ -10712,8 +10734,8 @@
       <c r="BY75" s="1"/>
     </row>
     <row r="76" spans="2:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC76" s="4"/>
-      <c r="BD76" s="5"/>
+      <c r="BC76" s="5"/>
+      <c r="BD76" s="6"/>
       <c r="BF76" s="1"/>
       <c r="BG76" s="1"/>
       <c r="BH76" s="1" t="s">
@@ -10752,10 +10774,10 @@
       </c>
       <c r="BX76" s="1"/>
       <c r="BY76" s="1"/>
-      <c r="CD76" s="2" t="s">
+      <c r="CD76" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="CE76" s="3"/>
+      <c r="CE76" s="4"/>
       <c r="CG76" s="1" t="s">
         <v>32</v>
       </c>
@@ -10800,8 +10822,8 @@
       <c r="CZ76" s="1"/>
     </row>
     <row r="77" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC77" s="6"/>
-      <c r="BD77" s="7"/>
+      <c r="BC77" s="7"/>
+      <c r="BD77" s="8"/>
       <c r="BF77" s="1"/>
       <c r="BG77" s="1"/>
       <c r="BH77" s="1"/>
@@ -10822,8 +10844,8 @@
       <c r="BW77" s="1"/>
       <c r="BX77" s="1"/>
       <c r="BY77" s="1"/>
-      <c r="CD77" s="4"/>
-      <c r="CE77" s="5"/>
+      <c r="CD77" s="5"/>
+      <c r="CE77" s="6"/>
       <c r="CG77" s="1"/>
       <c r="CH77" s="1"/>
       <c r="CI77" s="1" t="s">
@@ -10866,8 +10888,8 @@
       <c r="CZ77" s="1"/>
     </row>
     <row r="78" spans="2:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD78" s="4"/>
-      <c r="CE78" s="5"/>
+      <c r="CD78" s="5"/>
+      <c r="CE78" s="6"/>
       <c r="CG78" s="1"/>
       <c r="CH78" s="1"/>
       <c r="CI78" s="1"/>
@@ -10890,8 +10912,8 @@
       <c r="CZ78" s="1"/>
     </row>
     <row r="79" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD79" s="6"/>
-      <c r="CE79" s="7"/>
+      <c r="CD79" s="7"/>
+      <c r="CE79" s="8"/>
       <c r="CG79" s="1"/>
       <c r="CH79" s="1"/>
       <c r="CI79" s="1"/>
@@ -10913,85 +10935,332 @@
       <c r="CY79" s="1"/>
       <c r="CZ79" s="1"/>
     </row>
-    <row r="87" spans="55:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="2:104" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="BC81" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD81" s="4"/>
+      <c r="BF81" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="BG81" s="1"/>
+      <c r="BH81" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BI81" s="1"/>
+      <c r="BJ81" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BM81" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="BN81" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="BP81" s="1"/>
+      <c r="BQ81" s="1"/>
+      <c r="BR81" s="1"/>
+      <c r="BS81" s="1"/>
+      <c r="BT81" s="1"/>
+      <c r="BU81" s="1"/>
+      <c r="BV81" s="1"/>
+      <c r="BW81" s="1"/>
+      <c r="BX81" s="1"/>
+      <c r="BY81" s="1"/>
+    </row>
+    <row r="82" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="BC82" s="5"/>
+      <c r="BD82" s="6"/>
+      <c r="BF82" s="1"/>
+      <c r="BG82" s="1"/>
+      <c r="BH82" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BK82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BL82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BM82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BN82" s="1"/>
+      <c r="BO82" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="BP82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BQ82" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="BR82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BS82" s="1"/>
+      <c r="BT82" s="1"/>
+      <c r="BU82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BW82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BX82" s="1"/>
+      <c r="BY82" s="1"/>
+    </row>
+    <row r="83" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="BC83" s="5"/>
+      <c r="BD83" s="6"/>
+      <c r="BF83" s="1"/>
+      <c r="BG83" s="1"/>
+      <c r="BH83" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI83" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ83" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BK83" s="1"/>
+      <c r="BL83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BN83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BO83" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="BP83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BQ83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BR83" s="1"/>
+      <c r="BS83" s="1"/>
+      <c r="BT83" s="1"/>
+      <c r="BU83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BW83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BX83" s="1"/>
+      <c r="BY83" s="1"/>
+    </row>
+    <row r="84" spans="55:77" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BC84" s="7"/>
+      <c r="BD84" s="8"/>
+      <c r="BF84" s="1"/>
+      <c r="BG84" s="1"/>
+      <c r="BH84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="BI84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="BJ84" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="BK84" s="1"/>
+      <c r="BL84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BN84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BO84" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="BP84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BQ84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BR84" s="1"/>
+      <c r="BS84" s="1"/>
+      <c r="BT84" s="1"/>
+      <c r="BU84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BW84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BX84" s="1"/>
+      <c r="BY84" s="1"/>
+    </row>
+    <row r="86" spans="55:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="BC87" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="BD87" s="4"/>
+      <c r="BF87" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="BG87" s="1"/>
+      <c r="BH87" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BK87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BL87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BM87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BN87" s="1"/>
+      <c r="BO87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="BP87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BQ87" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="BR87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BS87" s="1"/>
+      <c r="BT87" s="1"/>
+      <c r="BU87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BW87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BX87" s="1"/>
+      <c r="BY87" s="1"/>
+    </row>
     <row r="88" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC88" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="BD88" s="3"/>
-      <c r="BF88" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="BC88" s="5"/>
+      <c r="BD88" s="6"/>
+      <c r="BF88" s="1"/>
       <c r="BG88" s="1"/>
       <c r="BH88" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI88" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="BI88" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="BJ88" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK88" s="1" t="s">
-        <v>3</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="BK88" s="1"/>
       <c r="BL88" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BM88" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BN88" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="BO88" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="BP88" s="1"/>
-      <c r="BQ88" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="BP88" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BQ88" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BR88" s="1"/>
       <c r="BS88" s="1"/>
       <c r="BT88" s="1"/>
-      <c r="BU88" s="1"/>
-      <c r="BV88" s="1"/>
-      <c r="BW88" s="1"/>
+      <c r="BU88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BW88" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="BX88" s="1"/>
       <c r="BY88" s="1"/>
     </row>
     <row r="89" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC89" s="4"/>
-      <c r="BD89" s="5"/>
+      <c r="BC89" s="5"/>
+      <c r="BD89" s="6"/>
       <c r="BF89" s="1"/>
       <c r="BG89" s="1"/>
       <c r="BH89" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BI89" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BJ89" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="BK89" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="BK89" s="1"/>
       <c r="BL89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BN89" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="BM89" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="BN89" s="1"/>
       <c r="BO89" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BP89" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BQ89" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="BR89" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="BR89" s="1"/>
       <c r="BS89" s="1"/>
       <c r="BT89" s="1"/>
       <c r="BU89" s="1" t="s">
@@ -11006,108 +11275,64 @@
       <c r="BX89" s="1"/>
       <c r="BY89" s="1"/>
     </row>
-    <row r="90" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC90" s="4"/>
-      <c r="BD90" s="5"/>
+    <row r="90" spans="55:77" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BC90" s="7"/>
+      <c r="BD90" s="8"/>
       <c r="BF90" s="1"/>
       <c r="BG90" s="1"/>
       <c r="BH90" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="BI90" s="1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BJ90" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="BK90" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="BK90" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="BL90" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BM90" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="BN90" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="BN90" s="1"/>
       <c r="BO90" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="BP90" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BQ90" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="BR90" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="BR90" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="BS90" s="1"/>
       <c r="BT90" s="1"/>
-      <c r="BU90" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BV90" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="BW90" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="BX90" s="1"/>
+      <c r="BU90" s="1">
+        <v>1</v>
+      </c>
+      <c r="BV90" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW90" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX90" s="1">
+        <v>0</v>
+      </c>
       <c r="BY90" s="1"/>
-    </row>
-    <row r="91" spans="55:77" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC91" s="6"/>
-      <c r="BD91" s="7"/>
-      <c r="BF91" s="1"/>
-      <c r="BG91" s="1"/>
-      <c r="BH91" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="BI91" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="BJ91" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="BK91" s="1"/>
-      <c r="BL91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BM91" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="BN91" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="BO91" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="BP91" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="BQ91" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="BR91" s="1"/>
-      <c r="BS91" s="1"/>
-      <c r="BT91" s="1"/>
-      <c r="BU91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BV91" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="BW91" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="BX91" s="1"/>
-      <c r="BY91" s="1"/>
     </row>
     <row r="96" spans="55:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="97" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC97" s="2" t="s">
+      <c r="BC97" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="BD97" s="3"/>
+      <c r="BD97" s="4"/>
       <c r="BF97" s="1" t="s">
         <v>32</v>
       </c>
@@ -11146,8 +11371,8 @@
       <c r="BY97" s="1"/>
     </row>
     <row r="98" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC98" s="4"/>
-      <c r="BD98" s="5"/>
+      <c r="BC98" s="5"/>
+      <c r="BD98" s="6"/>
       <c r="BF98" s="1"/>
       <c r="BG98" s="1"/>
       <c r="BH98" s="1" t="s">
@@ -11186,8 +11411,8 @@
       <c r="BY98" s="1"/>
     </row>
     <row r="99" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC99" s="4"/>
-      <c r="BD99" s="5"/>
+      <c r="BC99" s="5"/>
+      <c r="BD99" s="6"/>
       <c r="BF99" s="1"/>
       <c r="BG99" s="1"/>
       <c r="BH99" s="1" t="s">
@@ -11224,10 +11449,10 @@
       <c r="BW99" s="1"/>
       <c r="BX99" s="1"/>
       <c r="BY99" s="1"/>
-      <c r="CD99" s="2" t="s">
+      <c r="CD99" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="CE99" s="3"/>
+      <c r="CE99" s="4"/>
       <c r="CG99" s="1" t="s">
         <v>32</v>
       </c>
@@ -11266,8 +11491,8 @@
       <c r="CZ99" s="1"/>
     </row>
     <row r="100" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC100" s="6"/>
-      <c r="BD100" s="7"/>
+      <c r="BC100" s="7"/>
+      <c r="BD100" s="8"/>
       <c r="BF100" s="1"/>
       <c r="BG100" s="1"/>
       <c r="BH100" s="1" t="s">
@@ -11304,8 +11529,8 @@
       <c r="BW100" s="1"/>
       <c r="BX100" s="1"/>
       <c r="BY100" s="1"/>
-      <c r="CD100" s="4"/>
-      <c r="CE100" s="5"/>
+      <c r="CD100" s="5"/>
+      <c r="CE100" s="6"/>
       <c r="CG100" s="1"/>
       <c r="CH100" s="1"/>
       <c r="CI100" s="1" t="s">
@@ -11354,8 +11579,8 @@
       <c r="CZ100" s="1"/>
     </row>
     <row r="101" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD101" s="4"/>
-      <c r="CE101" s="5"/>
+      <c r="CD101" s="5"/>
+      <c r="CE101" s="6"/>
       <c r="CG101" s="1"/>
       <c r="CH101" s="1"/>
       <c r="CI101" s="1" t="s">
@@ -11408,10 +11633,10 @@
       <c r="CZ101" s="1"/>
     </row>
     <row r="102" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC102" s="2" t="s">
+      <c r="BC102" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="BD102" s="3"/>
+      <c r="BD102" s="4"/>
       <c r="BF102" s="1" t="s">
         <v>32</v>
       </c>
@@ -11450,8 +11675,8 @@
       <c r="BW102" s="1"/>
       <c r="BX102" s="1"/>
       <c r="BY102" s="1"/>
-      <c r="CD102" s="6"/>
-      <c r="CE102" s="7"/>
+      <c r="CD102" s="7"/>
+      <c r="CE102" s="8"/>
       <c r="CG102" s="1"/>
       <c r="CH102" s="1"/>
       <c r="CI102" s="1"/>
@@ -11474,8 +11699,8 @@
       <c r="CZ102" s="1"/>
     </row>
     <row r="103" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC103" s="4"/>
-      <c r="BD103" s="5"/>
+      <c r="BC103" s="5"/>
+      <c r="BD103" s="6"/>
       <c r="BF103" s="1"/>
       <c r="BG103" s="1"/>
       <c r="BH103" s="1" t="s">
@@ -11514,8 +11739,8 @@
       <c r="BY103" s="1"/>
     </row>
     <row r="104" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC104" s="4"/>
-      <c r="BD104" s="5"/>
+      <c r="BC104" s="5"/>
+      <c r="BD104" s="6"/>
       <c r="BF104" s="1"/>
       <c r="BG104" s="1"/>
       <c r="BH104" s="1" t="s">
@@ -11554,8 +11779,8 @@
       <c r="BY104" s="1"/>
     </row>
     <row r="105" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC105" s="6"/>
-      <c r="BD105" s="7"/>
+      <c r="BC105" s="7"/>
+      <c r="BD105" s="8"/>
       <c r="BF105" s="1"/>
       <c r="BG105" s="1"/>
       <c r="BH105" s="1"/>
@@ -11579,10 +11804,10 @@
     </row>
     <row r="108" spans="55:104" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC109" s="2" t="s">
+      <c r="BC109" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="BD109" s="3"/>
+      <c r="BD109" s="4"/>
       <c r="BF109" s="1" t="s">
         <v>32</v>
       </c>
@@ -11621,8 +11846,8 @@
       <c r="BY109" s="1"/>
     </row>
     <row r="110" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC110" s="4"/>
-      <c r="BD110" s="5"/>
+      <c r="BC110" s="5"/>
+      <c r="BD110" s="6"/>
       <c r="BF110" s="1"/>
       <c r="BG110" s="1"/>
       <c r="BH110" s="1" t="s">
@@ -11644,51 +11869,91 @@
         <v>24</v>
       </c>
       <c r="BN110" s="1"/>
-      <c r="BO110" s="1"/>
-      <c r="BP110" s="1"/>
-      <c r="BQ110" s="1"/>
-      <c r="BR110" s="1"/>
-      <c r="BS110" s="1"/>
-      <c r="BT110" s="1"/>
-      <c r="BU110" s="1" t="s">
+      <c r="BO110" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BP110" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ110" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="BR110" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS110" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="BT110" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BU110" s="1"/>
+      <c r="BV110" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="BV110" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="BW110" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="BX110" s="1"/>
       <c r="BY110" s="1"/>
     </row>
     <row r="111" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC111" s="4"/>
-      <c r="BD111" s="5"/>
+      <c r="BC111" s="5"/>
+      <c r="BD111" s="6"/>
       <c r="BF111" s="1"/>
       <c r="BG111" s="1"/>
-      <c r="BH111" s="1"/>
-      <c r="BI111" s="1"/>
-      <c r="BJ111" s="1"/>
-      <c r="BK111" s="1"/>
-      <c r="BL111" s="1"/>
+      <c r="BH111" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ111" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="BK111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL111" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="BM111" s="1"/>
-      <c r="BN111" s="1"/>
-      <c r="BO111" s="1"/>
-      <c r="BP111" s="1"/>
-      <c r="BQ111" s="1"/>
-      <c r="BR111" s="1"/>
-      <c r="BS111" s="1"/>
-      <c r="BT111" s="1"/>
-      <c r="BU111" s="1"/>
-      <c r="BV111" s="1"/>
-      <c r="BW111" s="1"/>
+      <c r="BN111" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="BO111" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="BP111" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="BQ111" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="BR111" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BS111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BT111" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BU111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BV111" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="BW111" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="BX111" s="1"/>
       <c r="BY111" s="1"/>
     </row>
     <row r="112" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC112" s="6"/>
-      <c r="BD112" s="7"/>
+      <c r="BC112" s="7"/>
+      <c r="BD112" s="8"/>
       <c r="BF112" s="1"/>
       <c r="BG112" s="1"/>
       <c r="BH112" s="1"/>
@@ -11712,10 +11977,10 @@
     </row>
     <row r="119" spans="55:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC120" s="2" t="s">
+      <c r="BC120" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="BD120" s="3"/>
+      <c r="BD120" s="4"/>
       <c r="BF120" s="1" t="s">
         <v>32</v>
       </c>
@@ -11754,8 +12019,8 @@
       <c r="BY120" s="1"/>
     </row>
     <row r="121" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC121" s="4"/>
-      <c r="BD121" s="5"/>
+      <c r="BC121" s="5"/>
+      <c r="BD121" s="6"/>
       <c r="BF121" s="1"/>
       <c r="BG121" s="1"/>
       <c r="BH121" s="1" t="s">
@@ -11812,8 +12077,8 @@
       </c>
     </row>
     <row r="122" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC122" s="4"/>
-      <c r="BD122" s="5"/>
+      <c r="BC122" s="5"/>
+      <c r="BD122" s="6"/>
       <c r="BF122" s="1"/>
       <c r="BG122" s="1"/>
       <c r="BH122" s="1" t="s">
@@ -11862,8 +12127,8 @@
       <c r="BY122" s="1"/>
     </row>
     <row r="123" spans="55:77" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC123" s="6"/>
-      <c r="BD123" s="7"/>
+      <c r="BC123" s="7"/>
+      <c r="BD123" s="8"/>
       <c r="BF123" s="1"/>
       <c r="BG123" s="1"/>
       <c r="BH123" s="1" t="s">
@@ -11909,10 +12174,10 @@
     </row>
     <row r="126" spans="55:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="127" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC127" s="2" t="s">
+      <c r="BC127" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="BD127" s="3"/>
+      <c r="BD127" s="4"/>
       <c r="BF127" s="1" t="s">
         <v>32</v>
       </c>
@@ -11965,8 +12230,8 @@
       <c r="BY127" s="1"/>
     </row>
     <row r="128" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC128" s="4"/>
-      <c r="BD128" s="5"/>
+      <c r="BC128" s="5"/>
+      <c r="BD128" s="6"/>
       <c r="BF128" s="1"/>
       <c r="BG128" s="1"/>
       <c r="BH128" s="1" t="s">
@@ -12019,8 +12284,8 @@
       <c r="BY128" s="1"/>
     </row>
     <row r="129" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC129" s="4"/>
-      <c r="BD129" s="5"/>
+      <c r="BC129" s="5"/>
+      <c r="BD129" s="6"/>
       <c r="BF129" s="1"/>
       <c r="BG129" s="1"/>
       <c r="BH129" s="1"/>
@@ -12043,8 +12308,8 @@
       <c r="BY129" s="1"/>
     </row>
     <row r="130" spans="55:77" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC130" s="6"/>
-      <c r="BD130" s="7"/>
+      <c r="BC130" s="7"/>
+      <c r="BD130" s="8"/>
       <c r="BF130" s="1"/>
       <c r="BG130" s="1"/>
       <c r="BH130" s="1"/>
@@ -12067,21 +12332,8 @@
       <c r="BY130" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="BC34:BD37"/>
-    <mergeCell ref="BC39:BD42"/>
-    <mergeCell ref="BC55:BD58"/>
-    <mergeCell ref="CD19:CE22"/>
-    <mergeCell ref="DE46:DF49"/>
-    <mergeCell ref="DE51:DF54"/>
-    <mergeCell ref="B67:C70"/>
-    <mergeCell ref="AB64:AC67"/>
-    <mergeCell ref="AB69:AC72"/>
-    <mergeCell ref="CD71:CE74"/>
-    <mergeCell ref="CD76:CE79"/>
-    <mergeCell ref="BC74:BD77"/>
-    <mergeCell ref="CD46:CE49"/>
-    <mergeCell ref="CD51:CE54"/>
+  <mergeCells count="31">
+    <mergeCell ref="BC87:BD90"/>
     <mergeCell ref="BC127:BD130"/>
     <mergeCell ref="CD28:CE31"/>
     <mergeCell ref="CD34:CE37"/>
@@ -12089,7 +12341,7 @@
     <mergeCell ref="DE23:DF26"/>
     <mergeCell ref="DE29:DF32"/>
     <mergeCell ref="DE35:DF38"/>
-    <mergeCell ref="BC88:BD91"/>
+    <mergeCell ref="BC81:BD84"/>
     <mergeCell ref="BC97:BD100"/>
     <mergeCell ref="BC102:BD105"/>
     <mergeCell ref="CD99:CE102"/>
@@ -12098,8 +12350,28 @@
     <mergeCell ref="CD59:CE62"/>
     <mergeCell ref="CD64:CE67"/>
     <mergeCell ref="BC68:BD71"/>
+    <mergeCell ref="B67:C70"/>
+    <mergeCell ref="AB64:AC67"/>
+    <mergeCell ref="AB69:AC72"/>
+    <mergeCell ref="CD71:CE74"/>
+    <mergeCell ref="CD76:CE79"/>
+    <mergeCell ref="BC74:BD77"/>
+    <mergeCell ref="BC34:BD37"/>
+    <mergeCell ref="BC39:BD42"/>
+    <mergeCell ref="BC55:BD58"/>
+    <mergeCell ref="CD19:CE22"/>
+    <mergeCell ref="DE46:DF49"/>
+    <mergeCell ref="DE51:DF54"/>
+    <mergeCell ref="CD46:CE49"/>
+    <mergeCell ref="CD51:CE54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{3f3ac890-09a1-47d3-8d04-15427d7fec91}" enabled="1" method="Standard" siteId="{39b77101-99b7-41c9-8d6a-7794b9d48476}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>